--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.27324103521851</v>
+        <v>1.994401668223007</v>
       </c>
       <c r="D2" t="n">
-        <v>28.16576355022509</v>
+        <v>4.576936576911578</v>
       </c>
       <c r="E2" t="n">
-        <v>14.54462664693523</v>
+        <v>2.363501830126975</v>
       </c>
       <c r="F2" t="n">
-        <v>12.67564863531747</v>
+        <v>2.059792903239088</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.70996060094065</v>
+        <v>3.040368597652855</v>
       </c>
       <c r="D3" t="n">
-        <v>32.26370302617865</v>
+        <v>5.242851741754031</v>
       </c>
       <c r="E3" t="n">
-        <v>14.54462664693523</v>
+        <v>2.363501830126975</v>
       </c>
       <c r="F3" t="n">
-        <v>12.67564863531747</v>
+        <v>2.059792903239088</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.78204094303372</v>
+        <v>1.752081653242979</v>
       </c>
       <c r="D4" t="n">
-        <v>10.1030713667582</v>
+        <v>1.641749097098207</v>
       </c>
       <c r="E4" t="n">
-        <v>14.54462664693523</v>
+        <v>2.363501830126975</v>
       </c>
       <c r="F4" t="n">
-        <v>12.67564863531747</v>
+        <v>2.059792903239088</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.79894005995904</v>
+        <v>7.604827759743345</v>
       </c>
       <c r="D5" t="n">
-        <v>45.56045940678645</v>
+        <v>7.403574653602798</v>
       </c>
       <c r="E5" t="n">
-        <v>14.54462664693523</v>
+        <v>2.363501830126975</v>
       </c>
       <c r="F5" t="n">
-        <v>12.67564863531747</v>
+        <v>2.059792903239088</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
